--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878287</v>
       </c>
       <c r="B4" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136879270</v>
       </c>
       <c r="B5" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136878287</v>
+        <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574553</v>
+        <v>574501</v>
       </c>
       <c r="R4" t="n">
-        <v>6338925</v>
+        <v>6338904</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,16 +980,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136878287</t>
+          <t>https://artportalen.se/Sighting/136878082</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136879270</v>
+        <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574456</v>
+        <v>574553</v>
       </c>
       <c r="R5" t="n">
-        <v>6338966</v>
+        <v>6338925</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,6 +1081,108 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136878192</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136879270</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80072</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skolehister, Skolehister, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>574456</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6338966</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136879270</t>
         </is>
@@ -1092,6 +1194,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136877692</v>
       </c>
       <c r="B2" t="n">
-        <v>97703</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136877997</v>
       </c>
       <c r="B3" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136879270</v>
       </c>
       <c r="B6" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37498-2026 artfynd.xlsx
+++ b/artfynd/A 37498-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136878082</v>
       </c>
       <c r="B4" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136878192</v>
       </c>
       <c r="B5" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
